--- a/Week 4 Submission/Workbooks/Defect_Log.xlsx
+++ b/Week 4 Submission/Workbooks/Defect_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gedion\Desktop\TrackWIL\06_Testing_Results_and_Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28173707-FC67-4359-8409-55B85518B075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A7836-9F99-416B-9497-E35CC3A491DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$103</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$105</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$L$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Tracker!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
   <si>
     <t>DEFECT / BUG LOG</t>
   </si>
@@ -141,21 +141,6 @@
     <t>The production build reports that Next.js 16.4.0 is affected by a known security vulnerability.</t>
   </si>
   <si>
-    <t>Moegammad Green</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Upgrade Next.js on a separate branch, rebuild and rerun npm run test:system before merging.</t>
-  </si>
-  <si>
-    <t>Not yet retested</t>
-  </si>
-  <si>
-    <t>npm run build output</t>
-  </si>
-  <si>
     <t>DEF-05</t>
   </si>
   <si>
@@ -168,10 +153,52 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Add lecturer@ctucareer.co.za / lecturer123 to the demo accounts box.</t>
-  </si>
-  <si>
-    <t>screenshots/01_login.png</t>
+    <t>Upgraded Next.js from 16.4.0 to 16.4.3 (eslint-config-next to match) on branch gedion/nextjs-security-upgrade. Commit 992573b, pull request #16.</t>
+  </si>
+  <si>
+    <t>Pass: the build no longer reports the advisory; npm audit finds 0 vulnerabilities; all 62 automated tests pass</t>
+  </si>
+  <si>
+    <t>evidence/system_test_run_2026-10-26.txt</t>
+  </si>
+  <si>
+    <t>The demo accounts box lists all five demo accounts, including the lecturer. Branch gedion/documents-docs-update.</t>
+  </si>
+  <si>
+    <t>Pass: TC-175</t>
+  </si>
+  <si>
+    <t>evidence/system_test_run_2026-10-26.txt; screenshots/01_login.png</t>
+  </si>
+  <si>
+    <t>DEF-06</t>
+  </si>
+  <si>
+    <t>New entry / edit placement pages</t>
+  </si>
+  <si>
+    <t>Opening the new entry page or the edit placement page showed an error screen: node:sqlite returns rows without a prototype, and React refuses to pass them from a Server Component to a Client Component. Reproduced on build 4c0ff41: HTTP 500.</t>
+  </si>
+  <si>
+    <t>The repository copies every row into a plain object; the timing test now also fails on any page error. Commit 2f3037d, pull request #12.</t>
+  </si>
+  <si>
+    <t>Pass: TC-156 (both pages 200); TC-144 reports no page errors</t>
+  </si>
+  <si>
+    <t>DEF-07</t>
+  </si>
+  <si>
+    <t>Access control</t>
+  </si>
+  <si>
+    <t>A role check only in an area's layout redirected the browser, but Next.js still rendered the page and sent its data in the body of the 307 response: a signed-in student, or anyone with a made-up session cookie, could read every student's name, email and hours from /coordinator. Reproduced on build 96ef01e.</t>
+  </si>
+  <si>
+    <t>Every protected page and layout calls requireRole() before it loads any data. Commit 899f600, pull request #14.</t>
+  </si>
+  <si>
+    <t>Pass: TC-171; TC-118, TC-119 and TC-121 now check the response body (they failed on the earlier build)</t>
   </si>
 </sst>
 </file>
@@ -270,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -292,6 +319,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,7 +630,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -780,7 +813,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>35</v>
       </c>
@@ -803,86 +836,134 @@
         <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8" s="6">
         <v>46318</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="B9" s="10">
+        <v>46321</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="135" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46321</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -1346,19 +1427,47 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
     </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:L103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:L105" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="E4:E43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E4:E45" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Low,Medium,High,Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F4:F43" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F4:F45" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I4:I43" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I4:I45" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Open,In Progress,Fixed,Retest,Closed"</formula1>
     </dataValidation>
   </dataValidations>
